--- a/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
+++ b/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
@@ -1,52 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Registro RAT Ley 21719" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro RAT Ley 21719" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -65,13 +42,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -396,315 +440,492 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="32.83203125" customWidth="1"/>
-    <col min="5" max="5" width="48.83203125" customWidth="1"/>
-    <col min="6" max="6" width="44.83203125" customWidth="1"/>
-    <col min="7" max="7" width="22.83203125" customWidth="1"/>
-    <col min="8" max="8" width="42.83203125" customWidth="1"/>
-    <col min="9" max="9" width="32.83203125" customWidth="1"/>
-    <col min="10" max="10" width="50.83203125" customWidth="1"/>
+    <col width="14.83203125" customWidth="1" min="1" max="1"/>
+    <col width="24.83203125" customWidth="1" min="2" max="2"/>
+    <col width="40.83203125" customWidth="1" min="3" max="3"/>
+    <col width="32.83203125" customWidth="1" min="4" max="4"/>
+    <col width="48.83203125" customWidth="1" min="5" max="5"/>
+    <col width="44.83203125" customWidth="1" min="6" max="6"/>
+    <col width="22.83203125" customWidth="1" min="7" max="7"/>
+    <col width="42.83203125" customWidth="1" min="8" max="8"/>
+    <col width="32.83203125" customWidth="1" min="9" max="9"/>
+    <col width="50.83203125" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>REGISTRO DE ACTIVIDADES DE TRATAMIENTO DE DATOS PERSONALES (RAT)</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>REGISTRO DE ACTIVIDADES DE TRATAMIENTO DE DATOS PERSONALES (RAT)</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Empresa Responsable:</v>
-      </c>
-      <c r="B3" t="str">
-        <v>[NOMBRE DE TU EMPRESA]</v>
-      </c>
-      <c r="C3" t="str">
-        <v>RUT:</v>
-      </c>
-      <c r="D3" t="str">
-        <v>[RUT EMPRESA]</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Fecha de Emisión / Actualización:</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Septiembre de 2026</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Empresa Responsable:</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>[NOMBRE DE TU EMPRESA]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RUT:</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>[RUT EMPRESA]</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Fecha de Emisión / Actualización:</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Septiembre de 2026</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Código RAT</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Área / Proceso</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Categoría de Datos Personales</v>
-      </c>
-      <c r="D5" t="str">
-        <v>Titulares Afectados</v>
-      </c>
-      <c r="E5" t="str">
-        <v>Finalidad del Tratamiento</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Base Legal de Licitud (Art. 13)</v>
-      </c>
-      <c r="G5" t="str">
-        <v>¿Datos Sensibles? (Art. 12)</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Destinatarios / Encargados Externos</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Plazo de Conservación</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Medidas de Seguridad Aplicadas (Art. 14 bis)</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Código RAT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Área / Proceso</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Categoría de Datos Personales</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Titulares Afectados</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Finalidad del Tratamiento</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Base Legal de Licitud (Art. 13)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>¿Datos Sensibles? (Art. 12)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Destinatarios / Encargados Externos</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Plazo de Conservación</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Medidas de Seguridad Aplicadas (Art. 14 bis)</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>RAT-01</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Recursos Humanos</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Nombre, RUT, sueldos, cuentas bancarias, domicilio, cotizaciones</v>
-      </c>
-      <c r="D6" t="str">
-        <v>Trabajadores activos y extrabajadores</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Liquidaciones de sueldo, transferencias bancarias, retención judicial pensión alimentos y pago en Previred</v>
-      </c>
-      <c r="F6" t="str">
-        <v>Cumplimiento contractual y mandato legal Código del Trabajo (Arts. 154 bis y ter)</v>
-      </c>
-      <c r="G6" t="str">
-        <v>NO</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Banco pagador, Software de Nómina, Previred, Dirección del Trabajo (portal Mi DT)</v>
-      </c>
-      <c r="I6" t="str">
-        <v>5 años tras término de relación laboral (prescripción laboral)</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Servidor cifrado, control de accesos con doble factor (2FA) y claves individuales</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RAT-01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Recursos Humanos</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Nombre, RUT, sueldos, cuentas bancarias, domicilio, cotizaciones</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Trabajadores activos y extrabajadores</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Liquidaciones de sueldo, transferencias bancarias, retención judicial pensión alimentos y pago en Previred</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Cumplimiento contractual y mandato legal Código del Trabajo (Arts. 154 bis y ter)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banco pagador, Software de Nómina, Previred, Dirección del Trabajo (portal Mi DT)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Hasta 5 años tras término relación laboral (Arts. 480 y 510 CT) y 6 años respaldo tributario/previsional (Art. 200 CTrib)</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Servidor cifrado, control de accesos con doble factor (2FA) y claves individuales</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>RAT-02</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Recursos Humanos</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Licencias médicas, diagnósticos de salud, exámenes ocupacionales</v>
-      </c>
-      <c r="D7" t="str">
-        <v>Trabajadores dependientes</v>
-      </c>
-      <c r="E7" t="str">
-        <v>Tramitación legal de subsidios por incapacidad ante COMPIN/Isapre y prevención de riesgos (Ley 16.744)</v>
-      </c>
-      <c r="F7" t="str">
-        <v>Obligación legal previsional y de salud pública (DFL 1, Min. Salud)</v>
-      </c>
-      <c r="G7" t="str">
-        <v>SÍ (Salud)</v>
-      </c>
-      <c r="H7" t="str">
-        <v>COMPIN, Isapres, Mutualidades de Seguridad. Prohibido acceso a jefaturas directas</v>
-      </c>
-      <c r="I7" t="str">
-        <v>5 años desde su tramitación legal</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Carpeta digital confidencial con acceso restringido exclusivo a Encargado RRHH</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RAT-02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Recursos Humanos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Licencias médicas, diagnósticos de salud, exámenes ocupacionales</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Trabajadores dependientes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Tramitación legal de subsidios por incapacidad ante COMPIN/Isapre y prevención de riesgos (Ley 16.744)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Obligación legal previsional y de salud pública (DFL 1, Min. Salud)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SÍ (Salud)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>COMPIN, Isapres, Mutualidades de Seguridad. Prohibido acceso a jefaturas directas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5 años desde su tramitación legal</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Carpeta digital confidencial con acceso restringido exclusivo a Encargado RRHH</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>RAT-03</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Operaciones &amp; RRHH</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Patrones biométricos encriptados (algoritmo huella digital o rostro)</v>
-      </c>
-      <c r="D8" t="str">
-        <v>Personal afecto a control de asistencia</v>
-      </c>
-      <c r="E8" t="str">
-        <v>Registro y control de jornada ordinaria y extraordinaria de trabajo</v>
-      </c>
-      <c r="F8" t="str">
-        <v>Cumplimiento legal Art. 33 Código del Trabajo y Res. Exenta N° 38/2024 de la Dirección del Trabajo</v>
-      </c>
-      <c r="G8" t="str">
-        <v>SÍ (Biométrico)</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Proveedor del reloj control de asistencia homologado y certificado ante la DT</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Durante la vigencia del contrato de trabajo</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Plantillas algorítmicas encriptadas sin fotos reales. Alternativa no biométrica obligatoria garantizada</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RAT-03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Operaciones &amp; RRHH</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Patrones biométricos encriptados (algoritmo huella digital o rostro)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Personal afecto a control de asistencia</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Registro y control de jornada ordinaria y extraordinaria de trabajo</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cumplimiento legal Art. 33 Código del Trabajo y Res. Exenta N° 38/2024 de la Dirección del Trabajo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SÍ (Biométrico)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Proveedor del reloj control de asistencia homologado y certificado ante la DT</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Durante la vigencia del contrato de trabajo</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Plantillas algorítmicas encriptadas sin fotos reales. Alternativa no biométrica obligatoria garantizada</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>RAT-04</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Ventas &amp; Facturación</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Nombre completo, RUT, dirección de entrega, correo, teléfono</v>
-      </c>
-      <c r="D9" t="str">
-        <v>Clientes compradores</v>
-      </c>
-      <c r="E9" t="str">
-        <v>Emisión de boletas y facturas electrónicas, cobranza y despacho logístico de productos</v>
-      </c>
-      <c r="F9" t="str">
-        <v>Ejecución contractual de compraventa y obligación tributaria ante el SII (Código Tributario)</v>
-      </c>
-      <c r="G9" t="str">
-        <v>NO</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Servicio de Impuestos Internos (SII), Pasarela de Pago, Couriers logísticos de despacho</v>
-      </c>
-      <c r="I9" t="str">
-        <v>6 años (Plazo de prescripción tributaria según normas del SII)</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Cifrado TLS/SSL en web, pasarela de pago certificada PCI-DSS compliance</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RAT-04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ventas &amp; Facturación</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Nombre completo, RUT, dirección de entrega, correo, teléfono</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Clientes compradores</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Emisión de boletas y facturas electrónicas, cobranza y despacho logístico de productos</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ejecución contractual de compraventa y obligación tributaria ante el SII (Código Tributario)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Servicio de Impuestos Internos (SII), Pasarela de Pago, Couriers logísticos de despacho</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6 años (Plazo de prescripción tributaria según normas del SII)</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Cifrado TLS/SSL en web, pasarela de pago certificada PCI-DSS compliance</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>RAT-05</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Marketing &amp; Comercial</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Nombre, correo electrónico, teléfono celular</v>
-      </c>
-      <c r="D10" t="str">
-        <v>Prospectos comerciales y clientes registrados</v>
-      </c>
-      <c r="E10" t="str">
-        <v>Envío de promociones comerciales, novedades del servicio y cotizaciones solicitadas</v>
-      </c>
-      <c r="F10" t="str">
-        <v>Consentimiento previo, expreso e informado del titular (Art. 13 letra c)</v>
-      </c>
-      <c r="G10" t="str">
-        <v>NO</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Plataforma de Email Marketing / CRM en la nube con contrato DPA firmado</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Hasta que el titular revoque su consentimiento (Derecho de Oposición ARCOP)</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Enlace directo y gratuito de desuscripción automática (opt-out) en cada comunicación</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RAT-05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Comercial</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nombre, correo electrónico, teléfono celular</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Prospectos comerciales y clientes registrados</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Envío de promociones comerciales, novedades del servicio y cotizaciones solicitadas</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Consentimiento previo, expreso e informado del titular (Art. 13 letra c)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Plataforma de Email Marketing / CRM en la nube con contrato DPA firmado</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Hasta que el titular revoque su consentimiento (Derecho de Oposición ARCOP)</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Enlace directo y gratuito de desuscripción automática (opt-out) en cada comunicación</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>RAT-06</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Seguridad de Instalaciones</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Imágenes y grabaciones de video en circuito cerrado (CCTV)</v>
-      </c>
-      <c r="D11" t="str">
-        <v>Colaboradores, clientes, proveedores y visitantes</v>
-      </c>
-      <c r="E11" t="str">
-        <v>Seguridad física de las instalaciones, control de accesos y prevención de delitos</v>
-      </c>
-      <c r="F11" t="str">
-        <v>Interés legítimo del responsable en la seguridad patrimonial y física (Art. 13 letra e)</v>
-      </c>
-      <c r="G11" t="str">
-        <v>NO</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Tribunales de Justicia o Ministerio Público (exclusivamente ante orden judicial formal)</v>
-      </c>
-      <c r="I11" t="str">
-        <v>30 días continuos (salvo investigación judicial o policial en curso)</v>
-      </c>
-      <c r="J11" t="str">
-        <v>Sobreescritura cíclica automática cada 30 días, servidor de video DVR bajo llave física</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RAT-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Seguridad de Instalaciones</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Imágenes y grabaciones de video en circuito cerrado (CCTV)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Colaboradores, clientes, proveedores y visitantes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Seguridad física de las instalaciones, control de accesos y prevención de delitos</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Interés legítimo del responsable en la seguridad patrimonial y física (Art. 13 letra e)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tribunales de Justicia o Ministerio Público (exclusivamente ante orden judicial formal)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30 días continuos (salvo investigación judicial o policial en curso)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sobreescritura cíclica automática cada 30 días, servidor de video DVR bajo llave física</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>INSTRUCCIONES OFICIALES DE CUMPLIMIENTO (LEY N° 21.719):</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INSTRUCCIONES OFICIALES DE CUMPLIMIENTO (LEY N° 21.719):</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>1. Obligatoriedad Legal:</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Conforme al Artículo 14 ter de la Ley 21.719, toda empresa que trate datos personales debe mantener este inventario actualizado.</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1. Obligatoriedad Legal:</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Conforme al Artículo 14 ter de la Ley 21.719, toda empresa que trate datos personales debe mantener este inventario actualizado.</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>2. Exhibición Fiscalizadora:</v>
-      </c>
-      <c r="B15" t="str">
-        <v>Este documento es lo primero que exige la Agencia de Protección de Datos Personales (APDP) ante una auditoría.</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2. Exhibición Fiscalizadora:</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Este documento es lo primero que exige la Agencia de Protección de Datos Personales (APDP) ante una auditoría.</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="str">
-        <v>3. Sanción por Omisión:</v>
-      </c>
-      <c r="B16" t="str">
-        <v>No contar con el Registro RAT constituye Infracción Grave (Art. 35 N° 2) sancionable con multa de hasta 10.000 UTM (~ millones de pesos).</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3. Sanción por Omisión:</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>No contar con el Registro RAT constituye Infracción Grave (Art. 35 N° 2) sancionable con multa de hasta 10.000 UTM (~ millones de pesos).</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="str">
-        <v>4. Personalización:</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Puedes agregar nuevas filas si tu empresa realiza otras actividades de tratamiento (por ejemplo, encuestas o geolocalización GPS).</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4. Personalización:</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Puedes agregar nuevas filas si tu empresa realiza otras actividades de tratamiento (por ejemplo, encuestas o geolocalización GPS).</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J17"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
+++ b/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
@@ -12,7 +12,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -20,16 +20,124 @@
       <sz val="12"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00E2E8F0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00059669"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00BE123C"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000369A1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E293B"/>
+        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F9FF"/>
+        <bgColor rgb="00F0F9FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000284C7"/>
+        <bgColor rgb="000284C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+        <bgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -37,12 +145,75 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -460,472 +631,513 @@
     <col width="50.83203125" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REGISTRO DE ACTIVIDADES DE TRATAMIENTO DE DATOS PERSONALES (RAT)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Inventario Oficial Obligatorio conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Empresa Responsable:</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>[NOMBRE DE TU EMPRESA]</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>RUT:</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>[RUT EMPRESA]</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>Fecha de Emisión / Actualización:</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Septiembre de 2026</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Código RAT</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Área / Proceso</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Categoría de Datos Personales</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Titulares Afectados</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Finalidad del Tratamiento</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Base Legal de Licitud (Art. 13)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>¿Datos Sensibles? (Art. 12)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Destinatarios / Encargados Externos</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Plazo de Conservación</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Medidas de Seguridad Aplicadas (Art. 14 bis)</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>RAT-01</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Nombre, RUT, sueldos, cuentas bancarias, domicilio, cotizaciones</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Trabajadores activos y extrabajadores</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Liquidaciones de sueldo, transferencias bancarias, retención judicial pensión alimentos y pago en Previred</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Cumplimiento contractual y mandato legal Código del Trabajo (Arts. 154 bis y ter)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Banco pagador, Software de Nómina, Previred, Dirección del Trabajo (portal Mi DT)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Hasta 5 años tras término relación laboral (Arts. 480 y 510 CT) y 6 años respaldo tributario/previsional (Art. 200 CTrib)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Servidor cifrado, control de accesos con doble factor (2FA) y claves individuales</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>RAT-02</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Licencias médicas, diagnósticos de salud, exámenes ocupacionales</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Trabajadores dependientes</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Tramitación legal de subsidios por incapacidad ante COMPIN/Isapre y prevención de riesgos (Ley 16.744)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Obligación legal previsional y de salud pública (DFL 1, Min. Salud)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>SÍ (Salud)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>COMPIN, Isapres, Mutualidades de Seguridad. Prohibido acceso a jefaturas directas</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>5 años desde su tramitación legal</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="12" t="inlineStr">
         <is>
           <t>Carpeta digital confidencial con acceso restringido exclusivo a Encargado RRHH</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>RAT-03</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Operaciones &amp; RRHH</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Patrones biométricos encriptados (algoritmo huella digital o rostro)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Personal afecto a control de asistencia</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Registro y control de jornada ordinaria y extraordinaria de trabajo</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Cumplimiento legal Art. 33 Código del Trabajo y Res. Exenta N° 38/2024 de la Dirección del Trabajo</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>SÍ (Biométrico)</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
         <is>
           <t>Proveedor del reloj control de asistencia homologado y certificado ante la DT</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Durante la vigencia del contrato de trabajo</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Plantillas algorítmicas encriptadas sin fotos reales. Alternativa no biométrica obligatoria garantizada</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>RAT-04</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>Ventas &amp; Facturación</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Nombre completo, RUT, dirección de entrega, correo, teléfono</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Clientes compradores</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Emisión de boletas y facturas electrónicas, cobranza y despacho logístico de productos</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>Ejecución contractual de compraventa y obligación tributaria ante el SII (Código Tributario)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Servicio de Impuestos Internos (SII), Pasarela de Pago, Couriers logísticos de despacho</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="12" t="inlineStr">
         <is>
           <t>6 años (Plazo de prescripción tributaria según normas del SII)</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>Cifrado TLS/SSL en web, pasarela de pago certificada PCI-DSS compliance</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>RAT-05</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Marketing &amp; Comercial</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Nombre, correo electrónico, teléfono celular</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Prospectos comerciales y clientes registrados</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Envío de promociones comerciales, novedades del servicio y cotizaciones solicitadas</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Consentimiento previo, expreso e informado del titular (Art. 13 letra c)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>Plataforma de Email Marketing / CRM en la nube con contrato DPA firmado</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>Hasta que el titular revoque su consentimiento (Derecho de Oposición ARCOP)</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Enlace directo y gratuito de desuscripción automática (opt-out) en cada comunicación</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="11" ht="55" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>RAT-06</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Seguridad de Instalaciones</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Imágenes y grabaciones de video en circuito cerrado (CCTV)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Colaboradores, clientes, proveedores y visitantes</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Seguridad física de las instalaciones, control de accesos y prevención de delitos</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Interés legítimo del responsable en la seguridad patrimonial y física (Art. 13 letra e)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Tribunales de Justicia o Ministerio Público (exclusivamente ante orden judicial formal)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="12" t="inlineStr">
         <is>
           <t>30 días continuos (salvo investigación judicial o policial en curso)</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>Sobreescritura cíclica automática cada 30 días, servidor de video DVR bajo llave física</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>INSTRUCCIONES OFICIALES DE CUMPLIMIENTO (LEY N° 21.719):</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>1. Obligatoriedad Legal:</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>Conforme al Artículo 14 ter de la Ley 21.719, toda empresa que trate datos personales debe mantener este inventario actualizado.</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="C14" s="19" t="n"/>
+      <c r="D14" s="19" t="n"/>
+      <c r="E14" s="19" t="n"/>
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>2. Exhibición Fiscalizadora:</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Este documento es lo primero que exige la Agencia de Protección de Datos Personales (APDP) ante una auditoría.</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="C15" s="19" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="19" t="n"/>
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>3. Sanción por Omisión:</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>No contar con el Registro RAT constituye Infracción Grave (Art. 35 N° 2) sancionable con multa de hasta 10.000 UTM (~ millones de pesos).</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="C16" s="19" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="19" t="n"/>
+      <c r="F16" s="19" t="n"/>
+      <c r="G16" s="19" t="n"/>
+      <c r="H16" s="19" t="n"/>
+      <c r="I16" s="19" t="n"/>
+      <c r="J16" s="19" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>4. Personalización:</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Puedes agregar nuevas filas si tu empresa realiza otras actividades de tratamiento (por ejemplo, encuestas o geolocalización GPS).</t>
         </is>
       </c>
+      <c r="C17" s="19" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="19" t="n"/>
+      <c r="F17" s="19" t="n"/>
+      <c r="G17" s="19" t="n"/>
+      <c r="H17" s="19" t="n"/>
+      <c r="I17" s="19" t="n"/>
+      <c r="J17" s="19" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
+++ b/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
@@ -1,90 +1,104 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registro RAT Ley 21719" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📌 Guía Rápida" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Registro RAT Oficial" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
-      <sz val="12"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00E2E8F0"/>
+      <color rgb="0094A3B8"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000284C7"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00CBD5E1"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
+      <color rgb="000284C7"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="000F172A"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="000F172A"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
       <b val="1"/>
       <color rgb="000284C7"/>
-      <sz val="10"/>
+      <sz val="9.5"/>
     </font>
     <font>
       <name val="Calibri"/>
       <color rgb="00059669"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00BE123C"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="000369A1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00334155"/>
-      <sz val="9.5"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="9">
@@ -97,43 +111,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000F172A"/>
-        <bgColor rgb="000F172A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E293B"/>
-        <bgColor rgb="001E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F9FF"/>
-        <bgColor rgb="00F0F9FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000284C7"/>
-        <bgColor rgb="000284C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
-        <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -163,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -171,54 +178,63 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -365,7 +381,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -400,7 +415,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -435,16 +449,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -566,46 +584,7 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
@@ -616,19 +595,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.83203125" customWidth="1" min="1" max="1"/>
-    <col width="24.83203125" customWidth="1" min="2" max="2"/>
-    <col width="40.83203125" customWidth="1" min="3" max="3"/>
-    <col width="32.83203125" customWidth="1" min="4" max="4"/>
-    <col width="48.83203125" customWidth="1" min="5" max="5"/>
-    <col width="44.83203125" customWidth="1" min="6" max="6"/>
-    <col width="22.83203125" customWidth="1" min="7" max="7"/>
-    <col width="42.83203125" customWidth="1" min="8" max="8"/>
-    <col width="32.83203125" customWidth="1" min="9" max="9"/>
-    <col width="50.83203125" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>GUÍA RÁPIDA: ¿QUÉ ES EL REGISTRO RAT Y CÓMO USARLO EN TU EMPRESA?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Inventario Legal Obligatorio exigido por el Artículo 14 ter de la Ley N° 21.719 de Protección de Datos Personales en Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1. ¿QUÉ ES ESTE DOCUMENTO EN PALABRAS SIMPLES?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="126" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Así como el SII le exige a tu empresa llevar un 'Libro de Compras y Ventas' para fiscalizar el dinero, la nueva Ley N° 21.719 exige llevar un 'Libro de Datos Personales' (el RAT).
+Es simplemente un inventario oficial donde dejas por escrito qué información de personas manejas (empleados, clientes, proveedores), con quién la compartes (contador, bancos, Previred) y cuántos años la guardas antes de borrarla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2. ¿POR QUÉ LA AUTORIDAD (O UN ABOGADO) TE LO VA A PEDIR?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="126" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Ante cualquier denuncia, inspección de la Dirección del Trabajo (DT) o auditoría de la nueva Agencia de Protección de Datos Personales (APDP), este Excel es el primer documento que te pedirán para comprobar si tu empresa cumple la ley.
+No tener el RAT constituye una 'Infracción Grave' que arriesga multas de hasta 10.000 UTM. Tenerlo al día demuestra diligencia y buena fe de la empresa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>3. ¿CÓMO SE USA ESTA PLANTILLA? (SOLO 3 PASOS):</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="144" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Paso 1: Ve a la siguiente pestaña: '📋 Registro RAT Oficial'.
+Paso 2: En la Fila 3, cambia [NOMBRE DE TU EMPRESA] por tu razón social y [RUT EMPRESA] por el RUT de tu negocio.
+Paso 3: ¡Listo! Las 6 filas ya vienen completamente rellenadas con los procesos habituales de una pyme chilena. No necesitas inventar nada. Guárdalo en tu computador o imprímelo para tu carpeta legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>4. RESUMEN DE LAS 6 FILAS PRE-LLENADAS EN LA SIGUIENTE PESTAÑA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="234" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>• RAT-01 (Sueldos y RRHH): Nombres, RUTs y cuentas bancarias de trabajadores para pagar sueldos y cotizaciones en Previred.
+• RAT-02 (Licencias Médicas): Gestión confidencial de salud ante COMPIN/Isapre (prohibido compartir con jefaturas directas).
+• RAT-03 (Reloj Control con Huella): Control de asistencia biométrico con alternativa no biométrica obligatoria (Res. Exenta 38 DT).
+• RAT-04 (Ventas y Boletas): Datos de clientes para emitir facturas/boletas al SII y coordinar envíos por courier.
+• RAT-05 (Marketing y WhatsApp): Datos comerciales con opción obligatoria de desuscripción voluntaria (opt-out).
+• RAT-06 (Cámaras de Seguridad CCTV): Grabaciones en video de vigilancia que se sobreescriben automáticamente cada 30 días.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A8:H8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -638,505 +732,422 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Inventario Oficial Obligatorio conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Empresa Responsable:</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>[NOMBRE DE TU EMPRESA]</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="n"/>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>[NOMBRE DE TU EMPRESA / RAZÓN SOCIAL]</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>RUT:</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>[RUT EMPRESA]</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Fecha de Emisión / Actualización:</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="H3" s="7" t="n"/>
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>Septiembre de 2026</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="J3" s="7" t="n"/>
+    </row>
+    <row r="4" ht="8" customHeight="1"/>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Código RAT</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Área / Proceso</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Categoría de Datos Personales</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Titulares Afectados</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>Finalidad del Tratamiento</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Base Legal de Licitud (Art. 13)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>¿Datos Sensibles? (Art. 12)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Destinatarios / Encargados Externos</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Plazo de Conservación</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Medidas de Seguridad Aplicadas (Art. 14 bis)</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="55" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>RAT-01</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Nombre, RUT, sueldos, cuentas bancarias, domicilio, cotizaciones</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Nombre, RUT, sueldos, cuentas bancarias, cotizaciones, domicilio</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>Trabajadores activos y extrabajadores</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>Liquidaciones de sueldo, transferencias bancarias, retención judicial pensión alimentos y pago en Previred</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Liquidaciones de sueldo, transferencias bancarias, retención judicial de pensión de alimentos y pago en Previred</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>Cumplimiento contractual y mandato legal Código del Trabajo (Arts. 154 bis y ter)</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>Banco pagador, Software de Nómina, Previred, Dirección del Trabajo (portal Mi DT)</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Hasta 5 años tras término relación laboral (Arts. 480 y 510 CT) y 6 años respaldo tributario/previsional (Art. 200 CTrib)</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Servidor cifrado, control de accesos con doble factor (2FA) y claves individuales</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>Servidor cifrado, control de accesos con doble factor (2FA) y claves individuales de usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>RAT-02</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Recursos Humanos</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Licencias médicas, diagnósticos de salud, exámenes ocupacionales</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Trabajadores dependientes</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="17" t="inlineStr">
         <is>
           <t>Tramitación legal de subsidios por incapacidad ante COMPIN/Isapre y prevención de riesgos (Ley 16.744)</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Obligación legal previsional y de salud pública (DFL 1, Min. Salud)</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>SÍ (Salud)</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>COMPIN, Isapres, Mutualidades de Seguridad. Prohibido acceso a jefaturas directas</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>5 años desde su tramitación legal</t>
         </is>
       </c>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Carpeta digital confidencial con acceso restringido exclusivo a Encargado RRHH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="J7" s="17" t="inlineStr">
+        <is>
+          <t>Carpeta digital confidencial con acceso restringido exclusivo al Encargado de RRHH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>RAT-03</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Operaciones &amp; RRHH</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Patrones biométricos encriptados (algoritmo huella digital o rostro)</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Patrones biométricos encriptados (algoritmo matemático huella o rostro)</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Personal afecto a control de asistencia</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Registro y control de jornada ordinaria y extraordinaria de trabajo</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>Cumplimiento legal Art. 33 Código del Trabajo y Res. Exenta N° 38/2024 de la Dirección del Trabajo</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="19" t="inlineStr">
         <is>
           <t>SÍ (Biométrico)</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>Proveedor del reloj control de asistencia homologado y certificado ante la DT</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>Durante la vigencia del contrato de trabajo</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>Plantillas algorítmicas encriptadas sin fotos reales. Alternativa no biométrica obligatoria garantizada</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="55" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>RAT-04</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Ventas &amp; Facturación</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Nombre completo, RUT, dirección de entrega, correo, teléfono</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>Clientes compradores</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Emisión de boletas y facturas electrónicas, cobranza y despacho logístico de productos</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
+        <is>
+          <t>Emisión de boletas y facturas electrónicas, cobranza y despacho logístico de pedidos</t>
+        </is>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>Ejecución contractual de compraventa y obligación tributaria ante el SII (Código Tributario)</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Servicio de Impuestos Internos (SII), Pasarela de Pago, Couriers logísticos de despacho</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>6 años (Plazo de prescripción tributaria según normas del SII)</t>
         </is>
       </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>Cifrado TLS/SSL en web, pasarela de pago certificada PCI-DSS compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="J9" s="17" t="inlineStr">
+        <is>
+          <t>Cifrado TLS/SSL en web, pasarela de pago certificada con estándar PCI-DSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>RAT-05</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Marketing &amp; Comercial</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Nombre, correo electrónico, teléfono celular</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Prospectos comerciales y clientes registrados</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Envío de promociones comerciales, novedades del servicio y cotizaciones solicitadas</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>Consentimiento previo, expreso e informado del titular (Art. 13 letra c)</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>Plataforma de Email Marketing / CRM en la nube con contrato DPA firmado</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>Hasta que el titular revoque su consentimiento (Derecho de Oposición ARCOP)</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>Enlace directo y gratuito de desuscripción automática (opt-out) en cada comunicación</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="55" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="54" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>RAT-06</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Seguridad de Instalaciones</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Seguridad Instalaciones</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Imágenes y grabaciones de video en circuito cerrado (CCTV)</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>Colaboradores, clientes, proveedores y visitantes</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="17" t="inlineStr">
         <is>
           <t>Seguridad física de las instalaciones, control de accesos y prevención de delitos</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>Interés legítimo del responsable en la seguridad patrimonial y física (Art. 13 letra e)</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Tribunales de Justicia o Ministerio Público (exclusivamente ante orden judicial formal)</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>30 días continuos (salvo investigación judicial o policial en curso)</t>
         </is>
       </c>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="J11" s="17" t="inlineStr">
         <is>
           <t>Sobreescritura cíclica automática cada 30 días, servidor de video DVR bajo llave física</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>INSTRUCCIONES OFICIALES DE CUMPLIMIENTO (LEY N° 21.719):</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>1. Obligatoriedad Legal:</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>Conforme al Artículo 14 ter de la Ley 21.719, toda empresa que trate datos personales debe mantener este inventario actualizado.</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="n"/>
-      <c r="D14" s="19" t="n"/>
-      <c r="E14" s="19" t="n"/>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
-      <c r="J14" s="19" t="n"/>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>2. Exhibición Fiscalizadora:</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>Este documento es lo primero que exige la Agencia de Protección de Datos Personales (APDP) ante una auditoría.</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="19" t="n"/>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>3. Sanción por Omisión:</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>No contar con el Registro RAT constituye Infracción Grave (Art. 35 N° 2) sancionable con multa de hasta 10.000 UTM (~ millones de pesos).</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="n"/>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="19" t="n"/>
-      <c r="F16" s="19" t="n"/>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="19" t="n"/>
-      <c r="J16" s="19" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>4. Personalización:</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>Puedes agregar nuevas filas si tu empresa realiza otras actividades de tratamiento (por ejemplo, encuestas o geolocalización GPS).</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="n"/>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="19" t="n"/>
-      <c r="F17" s="19" t="n"/>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
-      <c r="J17" s="19" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
+++ b/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📌 Guía Rápida" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Registro RAT Oficial" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Registro RAT" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -144,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -166,11 +166,55 @@
         <color rgb="00CBD5E1"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -230,6 +274,8 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -618,62 +664,115 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Inventario Legal Obligatorio exigido por el Artículo 14 ter de la Ley N° 21.719 de Protección de Datos Personales en Chile</t>
-        </is>
-      </c>
-    </row>
+          <t>Inventario de tratamientos de datos personales (Ley N° 19.628, modificada por la Ley N° 21.719)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1. ¿QUÉ ES ESTE DOCUMENTO EN PALABRAS SIMPLES?</t>
         </is>
       </c>
+      <c r="B4" s="21" t="n"/>
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="n"/>
+      <c r="F4" s="21" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="22" t="n"/>
     </row>
     <row r="5" ht="126" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Así como el SII le exige a tu empresa llevar un 'Libro de Compras y Ventas' para fiscalizar el dinero, la nueva Ley N° 21.719 exige llevar un 'Libro de Datos Personales' (el RAT).
-Es simplemente un inventario oficial donde dejas por escrito qué información de personas manejas (empleados, clientes, proveedores), con quién la compartes (contador, bancos, Previred) y cuántos años la guardas antes de borrarla.</t>
-        </is>
-      </c>
-    </row>
+          <t>Así como el SII le exige a tu empresa llevar un 'Libro de Compras y Ventas' para fiscalizar el dinero, la Ley N° 21.719 refuerza tus deberes de información y responsabilidad, y la forma práctica de cumplirlos es llevar un inventario de tus datos personales (el RAT).
+Es simplemente un inventario donde dejas por escrito qué información de personas manejas (empleados, clientes, proveedores), con quién la compartes (contador, bancos, Previred) y cuántos años la guardas antes de borrarla.</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="n"/>
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="n"/>
+      <c r="F5" s="21" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="22" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>2. ¿POR QUÉ LA AUTORIDAD (O UN ABOGADO) TE LO VA A PEDIR?</t>
-        </is>
-      </c>
+          <t>2. ¿PARA QUÉ SIRVE?</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="n"/>
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="n"/>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="22" t="n"/>
     </row>
     <row r="8" ht="126" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Ante cualquier denuncia, inspección de la Dirección del Trabajo (DT) o auditoría de la nueva Agencia de Protección de Datos Personales (APDP), este Excel es el primer documento que te pedirán para comprobar si tu empresa cumple la ley.
-No tener el RAT constituye una 'Infracción Grave' que arriesga multas de hasta 10.000 UTM. Tenerlo al día demuestra diligencia y buena fe de la empresa.</t>
-        </is>
-      </c>
-    </row>
+          <t>Ante un reclamo o una fiscalización de la Agencia de Protección de Datos Personales (APDP), este inventario te permite mostrar rápidamente qué datos tratas, para qué y por cuánto tiempo.
+Las infracciones a la ley se sancionan con multas de hasta 5.000, 10.000 o 20.000 UTM según sean leves, graves o gravísimas. Tenerlo al día demuestra diligencia y buena fe de la empresa.</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="n"/>
+      <c r="F8" s="21" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="22" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>3. ¿CÓMO SE USA ESTA PLANTILLA? (SOLO 3 PASOS):</t>
         </is>
       </c>
+      <c r="B10" s="21" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="22" t="n"/>
     </row>
     <row r="11" ht="144" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Paso 1: Ve a la siguiente pestaña: '📋 Registro RAT Oficial'.
+          <t>Paso 1: Ve a la siguiente pestaña: '📋 Registro RAT'.
 Paso 2: En la Fila 3, cambia [NOMBRE DE TU EMPRESA] por tu razón social y [RUT EMPRESA] por el RUT de tu negocio.
-Paso 3: ¡Listo! Las 6 filas ya vienen completamente rellenadas con los procesos habituales de una pyme chilena. No necesitas inventar nada. Guárdalo en tu computador o imprímelo para tu carpeta legal.</t>
-        </is>
-      </c>
-    </row>
+Paso 3: Revisa las 6 filas: vienen completadas con los procesos habituales de una pyme chilena; ajústalas a tu realidad (agrega o elimina filas). Guárdalo en tu computador o imprímelo para tu carpeta.</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="21" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="22" t="n"/>
+    </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>4. RESUMEN DE LAS 6 FILAS PRE-LLENADAS EN LA SIGUIENTE PESTAÑA:</t>
         </is>
       </c>
+      <c r="B13" s="21" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="21" t="n"/>
+      <c r="G13" s="21" t="n"/>
+      <c r="H13" s="22" t="n"/>
     </row>
     <row r="14" ht="234" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -686,6 +785,13 @@
 • RAT-06 (Cámaras de Seguridad CCTV): Grabaciones en video de vigilancia que se sobreescriben automáticamente cada 30 días.</t>
         </is>
       </c>
+      <c r="B14" s="21" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="22" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -735,7 +841,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Conforme al Artículo 14 ter de la Ley N° 21.719 - Agencia de Protección de Datos Personales (APDP) Chile</t>
+          <t>Ley N° 19.628, modificada por la Ley N° 21.719</t>
         </is>
       </c>
     </row>
@@ -745,13 +851,13 @@
           <t>Empresa Responsable:</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n"/>
+      <c r="B3" s="22" t="n"/>
       <c r="C3" s="8" t="inlineStr">
         <is>
           <t>[NOMBRE DE TU EMPRESA / RAZÓN SOCIAL]</t>
         </is>
       </c>
-      <c r="D3" s="7" t="n"/>
+      <c r="D3" s="22" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
           <t>RUT:</t>
@@ -767,13 +873,13 @@
           <t>Fecha de Emisión / Actualización:</t>
         </is>
       </c>
-      <c r="H3" s="7" t="n"/>
+      <c r="H3" s="22" t="n"/>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>Septiembre de 2026</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="n"/>
+          <t>[MES Y AÑO]</t>
+        </is>
+      </c>
+      <c r="J3" s="22" t="n"/>
     </row>
     <row r="4" ht="8" customHeight="1"/>
     <row r="5" ht="32" customHeight="1">
@@ -804,12 +910,12 @@
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>Base Legal de Licitud (Art. 13)</t>
+          <t>Base Legal de Licitud</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>¿Datos Sensibles? (Art. 12)</t>
+          <t>¿Datos Sensibles?</t>
         </is>
       </c>
       <c r="H5" s="10" t="inlineStr">
@@ -824,7 +930,7 @@
       </c>
       <c r="J5" s="10" t="inlineStr">
         <is>
-          <t>Medidas de Seguridad Aplicadas (Art. 14 bis)</t>
+          <t>Medidas de Seguridad Aplicadas</t>
         </is>
       </c>
     </row>
@@ -856,7 +962,7 @@
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Cumplimiento contractual y mandato legal Código del Trabajo (Arts. 154 bis y ter)</t>
+          <t>Cumplimiento contractual y mandato legal Código del Trabajo (Art. 154 ter)</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -871,7 +977,7 @@
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>Hasta 5 años tras término relación laboral (Arts. 480 y 510 CT) y 6 años respaldo tributario/previsional (Art. 200 CTrib)</t>
+          <t>Hasta 5 años tras término relación laboral y 6 años respaldo tributario/previsional (Art. 200 CTrib)</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
@@ -970,7 +1076,7 @@
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>Proveedor del reloj control de asistencia homologado y certificado ante la DT</t>
+          <t>Proveedor del sistema de control de asistencia (Res. Exenta N° 38/2024 DT)</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -1064,7 +1170,7 @@
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Consentimiento previo, expreso e informado del titular (Art. 13 letra c)</t>
+          <t>Consentimiento previo, expreso e informado del titular</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1116,7 +1222,7 @@
       </c>
       <c r="F11" s="17" t="inlineStr">
         <is>
-          <t>Interés legítimo del responsable en la seguridad patrimonial y física (Art. 13 letra e)</t>
+          <t>Interés legítimo del responsable en la seguridad patrimonial y física</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">

--- a/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
+++ b/api/assets/kit_datos_files/4_Registro_Actividades_Tratamiento_RAT_Ley_21719.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📌 Guía Rápida" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 Registro RAT" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="➕ Fila nueva" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,8 +101,84 @@
       <color rgb="00BE123C"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000382E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="0000382E"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00047857"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFE2E8F0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000382E"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0000382E"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -141,6 +218,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000382E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000261F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECF5F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3B0"/>
       </patternFill>
     </fill>
   </fills>
@@ -214,7 +311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -276,6 +373,94 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -639,174 +824,606 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>GUÍA RÁPIDA: ¿QUÉ ES EL REGISTRO RAT Y CÓMO USARLO EN TU EMPRESA?</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Inventario de tratamientos de datos personales (Ley N° 19.628, modificada por la Ley N° 21.719)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>GUÍA RÁPIDA: CÓMO COMPLETAR TU REGISTRO RAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>Léela una vez (3 minutos). Después trabaja en la pestaña «Registro RAT».</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1. ¿QUÉ ES ESTE DOCUMENTO EN PALABRAS SIMPLES?</t>
-        </is>
-      </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
-      <c r="F4" s="21" t="n"/>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="22" t="n"/>
-    </row>
-    <row r="5" ht="126" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Así como el SII le exige a tu empresa llevar un 'Libro de Compras y Ventas' para fiscalizar el dinero, la Ley N° 21.719 refuerza tus deberes de información y responsabilidad, y la forma práctica de cumplirlos es llevar un inventario de tus datos personales (el RAT).
-Es simplemente un inventario donde dejas por escrito qué información de personas manejas (empleados, clientes, proveedores), con quién la compartes (contador, bancos, Previred) y cuántos años la guardas antes de borrarla.</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="21" t="n"/>
-      <c r="E5" s="21" t="n"/>
-      <c r="F5" s="21" t="n"/>
-      <c r="G5" s="21" t="n"/>
-      <c r="H5" s="22" t="n"/>
-    </row>
-    <row r="6"/>
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>1. ¿QUÉ ES ESTE ARCHIVO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="26" t="inlineStr">
+        <is>
+          <t>El RAT (Registro de Actividades de Tratamiento) es un inventario: una tabla donde dejas por escrito qué datos de personas maneja tu empresa (de trabajadores, clientes, proveedores), para qué los usas, con quién los compartes y cuánto tiempo los guardas.
+Es como el libro de compras y ventas, pero de datos personales. Sirve para mostrar orden si la Agencia de Protección de Datos Personales te pregunta o recibes un reclamo.</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>2. ¿PARA QUÉ SIRVE?</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="n"/>
-      <c r="C7" s="21" t="n"/>
-      <c r="D7" s="21" t="n"/>
-      <c r="E7" s="21" t="n"/>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="22" t="n"/>
-    </row>
-    <row r="8" ht="126" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Ante un reclamo o una fiscalización de la Agencia de Protección de Datos Personales (APDP), este inventario te permite mostrar rápidamente qué datos tratas, para qué y por cuánto tiempo.
-Las infracciones a la ley se sancionan con multas de hasta 5.000, 10.000 o 20.000 UTM según sean leves, graves o gravísimas. Tenerlo al día demuestra diligencia y buena fe de la empresa.</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="n"/>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="21" t="n"/>
-      <c r="G8" s="21" t="n"/>
-      <c r="H8" s="22" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>2. ¿LO TENGO QUE ENVIAR A ALGUIEN?</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48.5" customHeight="1">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>No. No se envía a ninguna institución. Lo guardas tú, en la carpeta de administración, y lo muestras solo si la Agencia de Protección de Datos o la Dirección del Trabajo te lo piden.
+Casi todo viene ya escrito con los casos típicos de una pyme chilena: tú completas 3 celdas y ajustas lo que sea distinto.</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>3. ¿CÓMO SE USA ESTA PLANTILLA? (SOLO 3 PASOS):</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
-      <c r="G10" s="21" t="n"/>
-      <c r="H10" s="22" t="n"/>
-    </row>
-    <row r="11" ht="144" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Paso 1: Ve a la siguiente pestaña: '📋 Registro RAT'.
-Paso 2: En la Fila 3, cambia [NOMBRE DE TU EMPRESA] por tu razón social y [RUT EMPRESA] por el RUT de tu negocio.
-Paso 3: Revisa las 6 filas: vienen completadas con los procesos habituales de una pyme chilena; ajústalas a tu realidad (agrega o elimina filas). Guárdalo en tu computador o imprímelo para tu carpeta.</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
-      <c r="G11" s="21" t="n"/>
-      <c r="H11" s="22" t="n"/>
-    </row>
-    <row r="12"/>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>4. RESUMEN DE LAS 6 FILAS PRE-LLENADAS EN LA SIGUIENTE PESTAÑA:</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="21" t="n"/>
-      <c r="E13" s="21" t="n"/>
-      <c r="F13" s="21" t="n"/>
-      <c r="G13" s="21" t="n"/>
-      <c r="H13" s="22" t="n"/>
-    </row>
-    <row r="14" ht="234" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• RAT-01 (Sueldos y RRHH): Nombres, RUTs y cuentas bancarias de trabajadores para pagar sueldos y cotizaciones en Previred.
-• RAT-02 (Licencias Médicas): Gestión confidencial de salud ante COMPIN/Isapre (prohibido compartir con jefaturas directas).
-• RAT-03 (Reloj Control con Huella): Control de asistencia biométrico con alternativa no biométrica obligatoria (Res. Exenta 38 DT).
-• RAT-04 (Ventas y Boletas): Datos de clientes para emitir facturas/boletas al SII y coordinar envíos por courier.
-• RAT-05 (Marketing y WhatsApp): Datos comerciales con opción obligatoria de desuscripción voluntaria (opt-out).
-• RAT-06 (Cámaras de Seguridad CCTV): Grabaciones en video de vigilancia que se sobreescriben automáticamente cada 30 días.</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="22" t="n"/>
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>3. LO QUE TIENES QUE HACER (5 PASOS, ~15 MINUTOS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21.5" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Paso 1</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="inlineStr">
+        <is>
+          <t>Abre la pestaña «Registro RAT» (abajo, junto a esta).</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="28" t="n"/>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Paso 2</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Completa las 3 celdas amarillas de la fila 3:
+• C3: razón social de tu empresa
+• F3: RUT de la empresa
+• I3: mes y año de hoy (por ejemplo «Octubre 2026»).</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="28" t="n"/>
+    </row>
+    <row r="13" ht="75.5" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Paso 3</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="inlineStr">
+        <is>
+          <t>Recorre las filas RAT-01 a RAT-06 y pregúntate en cada una: «¿mi empresa hace esto?»
+• SÍ → déjala y corrige lo que sea distinto en tu caso (mira la sección 5).
+• NO → bórrala: clic derecho sobre el número de la fila → Eliminar.
+• Si hay algo que tu empresa hace y no aparece (por ejemplo, GPS en las camionetas): copia la fila de la pestaña «Fila nueva» a la tabla y cámbiale los textos.</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="28" t="n"/>
+    </row>
+    <row r="14" ht="35" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Paso 4</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="inlineStr">
+        <is>
+          <t>Revisa que cada fila diga solo lo que es verdad en tu empresa, sobre todo «Medidas de seguridad»: no dejes escrito doble factor, cifrado ni certificaciones que no tengas.</t>
+        </is>
+      </c>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="28" t="n"/>
+    </row>
+    <row r="15" ht="35" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Paso 5</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>Guarda el archivo (y, si quieres, también un PDF o una impresión) en la carpeta de administración. Vuelve a abrirlo y cambia la fecha cuando algo cambie: un software nuevo, un proveedor nuevo, una cámara nueva.</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="28" t="n"/>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>4. QUÉ SIGNIFICA CADA COLUMNA DE LA TABLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>Columna</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>Qué escribir</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>Ejemplo</t>
+        </is>
+      </c>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+    </row>
+    <row r="19" ht="35" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Código RAT</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Un número correlativo para ubicar la fila.</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>RAT-01, RAT-02… Si agregas una fila, sigue la numeración: RAT-07.</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="n"/>
+      <c r="H19" s="32" t="n"/>
+    </row>
+    <row r="20" ht="21.5" customHeight="1">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Área / Proceso</t>
+        </is>
+      </c>
+      <c r="B20" s="34" t="inlineStr">
+        <is>
+          <t>La parte de tu empresa que usa esos datos.</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="n"/>
+      <c r="D20" s="35" t="n"/>
+      <c r="E20" s="35" t="n"/>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>Recursos Humanos, Ventas, Bodega, Administración.</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="n"/>
+      <c r="H20" s="35" t="n"/>
+    </row>
+    <row r="21" ht="35" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Categoría de Datos Personales</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Qué datos concretos guardas (los campos o papeles).</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n"/>
+      <c r="D21" s="32" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Nombre, RUT, correo, teléfono, dirección, cuenta bancaria.</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="n"/>
+      <c r="H21" s="32" t="n"/>
+    </row>
+    <row r="22" ht="21.5" customHeight="1">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>Titulares Afectados</t>
+        </is>
+      </c>
+      <c r="B22" s="34" t="inlineStr">
+        <is>
+          <t>De quién son esos datos.</t>
+        </is>
+      </c>
+      <c r="C22" s="35" t="n"/>
+      <c r="D22" s="35" t="n"/>
+      <c r="E22" s="35" t="n"/>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>Trabajadores, clientes, proveedores, visitantes.</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n"/>
+      <c r="H22" s="35" t="n"/>
+    </row>
+    <row r="23" ht="21.5" customHeight="1">
+      <c r="A23" s="30" t="inlineStr">
+        <is>
+          <t>Finalidad del Tratamiento</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>Para qué los usas, en una frase.</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n"/>
+      <c r="D23" s="32" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Emitir boletas y despachar pedidos.</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="n"/>
+      <c r="H23" s="32" t="n"/>
+    </row>
+    <row r="24" ht="35" customHeight="1">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Base Legal de Licitud</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="inlineStr">
+        <is>
+          <t>Por qué puedes usarlos. Las más comunes: contrato, obligación legal, consentimiento, interés legítimo.</t>
+        </is>
+      </c>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>Ejecución del contrato de compraventa y obligación tributaria.</t>
+        </is>
+      </c>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="62" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>¿Datos Sensibles?</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>SÍ si son de salud, biometría (huella, rostro) u otros muy personales (ideología, religión, afiliación sindical, vida sexual, origen étnico). Si trabajas con datos de menores de edad, anótalo también: la ley les da protección especial. Si no, NO.</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n"/>
+      <c r="D25" s="32" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Licencias médicas = SÍ (Salud). Boletas de venta = NO.</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="n"/>
+      <c r="H25" s="32" t="n"/>
+    </row>
+    <row r="26" ht="35" customHeight="1">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>Destinatarios / Encargados Externos</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="inlineStr">
+        <is>
+          <t>Con quién compartes los datos: instituciones y proveedores.</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="n"/>
+      <c r="D26" s="35" t="n"/>
+      <c r="E26" s="35" t="n"/>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>Banco, Previred, SII, Transbank o Flow, courier, contador.</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n"/>
+      <c r="H26" s="35" t="n"/>
+    </row>
+    <row r="27" ht="35" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>Plazo de Conservación</t>
+        </is>
+      </c>
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>Cuánto tiempo los guardas antes de borrarlos. Si no sabes, deja el que viene.</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="n"/>
+      <c r="D27" s="32" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>6 años (respaldo tributario).</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="n"/>
+      <c r="H27" s="32" t="n"/>
+    </row>
+    <row r="28" ht="35" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Medidas de Seguridad Aplicadas</t>
+        </is>
+      </c>
+      <c r="B28" s="34" t="inlineStr">
+        <is>
+          <t>Cómo proteges los datos en la práctica. Escribe solo lo que de verdad haces.</t>
+        </is>
+      </c>
+      <c r="C28" s="35" t="n"/>
+      <c r="D28" s="35" t="n"/>
+      <c r="E28" s="35" t="n"/>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>Claves individuales, archivador con llave, respaldo semanal, antivirus.</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="n"/>
+      <c r="H28" s="35" t="n"/>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>5. QUÉ CAMBIAR EN CADA FILA YA RELLENA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="35" customHeight="1">
+      <c r="A31" s="36" t="inlineStr">
+        <is>
+          <t>RAT-01 · Sueldos y RR.HH.</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>Cambia «Banco pagador» y «Software de Nómina» por el banco y el programa que usas de verdad (Buk, Talana, una planilla Excel…). Revisa «Medidas de seguridad»: deja solo las que aplicas.</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="32" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="32" t="n"/>
+      <c r="H31" s="32" t="n"/>
+    </row>
+    <row r="32" ht="35" customHeight="1">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>RAT-02 · Licencias médicas</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="inlineStr">
+        <is>
+          <t>Déjala si tienes trabajadores. Revisa que quien las ve sea solo RR.HH. (o quien tramita las licencias) y ajusta la mutual o Isapre si corresponde.</t>
+        </is>
+      </c>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="35" t="n"/>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="G32" s="35" t="n"/>
+      <c r="H32" s="35" t="n"/>
+    </row>
+    <row r="33" ht="35" customHeight="1">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>RAT-03 · Reloj control con huella o rostro</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>Si NO usas huella ni rostro, bórrala (la tarjeta, la clave o el libro no son biométricos). Si la usas: escribe el nombre del proveedor del reloj.</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n"/>
+      <c r="D33" s="32" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="32" t="n"/>
+      <c r="H33" s="32" t="n"/>
+    </row>
+    <row r="34" ht="35" customHeight="1">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>RAT-04 · Ventas y boletas</t>
+        </is>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>Anota tu pasarela de pago real (Transbank, Flow, Mercado Pago…) y tus couriers. Si vendes solo a empresas, ajusta «Titulares».</t>
+        </is>
+      </c>
+      <c r="C34" s="35" t="n"/>
+      <c r="D34" s="35" t="n"/>
+      <c r="E34" s="35" t="n"/>
+      <c r="F34" s="35" t="n"/>
+      <c r="G34" s="35" t="n"/>
+      <c r="H34" s="35" t="n"/>
+    </row>
+    <row r="35" ht="35" customHeight="1">
+      <c r="A35" s="36" t="inlineStr">
+        <is>
+          <t>RAT-05 · Marketing y WhatsApp</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Si no envías promociones, bórrala. Si las envías: escribe tu herramienta (Mailchimp, WhatsApp Business…) y confirma que cada mensaje deja darse de baja.</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="32" t="n"/>
+      <c r="H35" s="32" t="n"/>
+    </row>
+    <row r="36" ht="35" customHeight="1">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>RAT-06 · Cámaras de seguridad</t>
+        </is>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>Si no tienes cámaras, bórrala. Si las tienes: cambia «30 días» por el tiempo real que graba tu equipo.</t>
+        </is>
+      </c>
+      <c r="C36" s="35" t="n"/>
+      <c r="D36" s="35" t="n"/>
+      <c r="E36" s="35" t="n"/>
+      <c r="F36" s="35" t="n"/>
+      <c r="G36" s="35" t="n"/>
+      <c r="H36" s="35" t="n"/>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>6. SI AÚN NO TIENES EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="35" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>Puedes usar el archivo como ejemplo ya resuelto de cómo se ve un RAT: no hay nada que enviar ni registrar. Cuando tengas la empresa, sigue los pasos de la sección 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="33" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>Modelo de referencia basado en la normativa vigente a octubre de 2026; no constituye asesoría legal. Si tu caso tiene particularidades, revísalo con un abogado antes de usarlo. La Ley 21.719 rige desde el 1 de diciembre de 2026.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="45">
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B24:E24"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B27:E27"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B11:H11"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="F24:H24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="29" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -814,7 +1431,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -832,110 +1449,116 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="39" t="inlineStr">
         <is>
           <t>REGISTRO DE ACTIVIDADES DE TRATAMIENTO DE DATOS PERSONALES (RAT)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>Ley N° 19.628, modificada por la Ley N° 21.719</t>
         </is>
       </c>
     </row>
     <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>Empresa Responsable:</t>
         </is>
       </c>
       <c r="B3" s="22" t="n"/>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="42" t="inlineStr">
         <is>
           <t>[NOMBRE DE TU EMPRESA / RAZÓN SOCIAL]</t>
         </is>
       </c>
       <c r="D3" s="22" t="n"/>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>RUT:</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="42" t="inlineStr">
         <is>
           <t>[RUT EMPRESA]</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="41" t="inlineStr">
         <is>
           <t>Fecha de Emisión / Actualización:</t>
         </is>
       </c>
       <c r="H3" s="22" t="n"/>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="42" t="inlineStr">
         <is>
           <t>[MES Y AÑO]</t>
         </is>
       </c>
       <c r="J3" s="22" t="n"/>
     </row>
-    <row r="4" ht="8" customHeight="1"/>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>Celdas amarillas = complétalas. Revisa cada fila (la pestaña «Guía Rápida» explica cómo): déjala si tu empresa lo hace, ajusta lo distinto y borra las filas que no aplican.</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>Código RAT</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="44" t="inlineStr">
         <is>
           <t>Área / Proceso</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="44" t="inlineStr">
         <is>
           <t>Categoría de Datos Personales</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D5" s="44" t="inlineStr">
         <is>
           <t>Titulares Afectados</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="44" t="inlineStr">
         <is>
           <t>Finalidad del Tratamiento</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="F5" s="44" t="inlineStr">
         <is>
           <t>Base Legal de Licitud</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="44" t="inlineStr">
         <is>
           <t>¿Datos Sensibles?</t>
         </is>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="H5" s="44" t="inlineStr">
         <is>
           <t>Destinatarios / Encargados Externos</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="44" t="inlineStr">
         <is>
           <t>Plazo de Conservación</t>
         </is>
       </c>
-      <c r="J5" s="10" t="inlineStr">
+      <c r="J5" s="44" t="inlineStr">
         <is>
           <t>Medidas de Seguridad Aplicadas</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="45" t="inlineStr">
         <is>
           <t>RAT-01</t>
         </is>
@@ -965,7 +1588,7 @@
           <t>Cumplimiento contractual y mandato legal Código del Trabajo (Art. 154 ter)</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -987,7 +1610,7 @@
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>RAT-02</t>
         </is>
@@ -1039,7 +1662,7 @@
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="45" t="inlineStr">
         <is>
           <t>RAT-03</t>
         </is>
@@ -1091,7 +1714,7 @@
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="47" t="inlineStr">
         <is>
           <t>RAT-04</t>
         </is>
@@ -1121,7 +1744,7 @@
           <t>Ejecución contractual de compraventa y obligación tributaria ante el SII (Código Tributario)</t>
         </is>
       </c>
-      <c r="G9" s="20" t="inlineStr">
+      <c r="G9" s="48" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1143,7 +1766,7 @@
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="45" t="inlineStr">
         <is>
           <t>RAT-05</t>
         </is>
@@ -1173,7 +1796,7 @@
           <t>Consentimiento previo, expreso e informado del titular</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="46" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1195,7 +1818,7 @@
       </c>
     </row>
     <row r="11" ht="54" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="47" t="inlineStr">
         <is>
           <t>RAT-06</t>
         </is>
@@ -1225,7 +1848,7 @@
           <t>Interés legítimo del responsable en la seguridad patrimonial y física</t>
         </is>
       </c>
-      <c r="G11" s="20" t="inlineStr">
+      <c r="G11" s="48" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1247,8 +1870,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A4:J4"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="A3:B3"/>
@@ -1256,5 +1880,207 @@
     <mergeCell ref="I3:J3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="49" t="inlineStr">
+        <is>
+          <t>FILA NUEVA: MODELO PARA AGREGAR UNA ACTIVIDAD QUE NO ESTÁ EN LA TABLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Copia la fila de abajo, pégala en la primera fila vacía de «Registro RAT» (debajo de la última) y cambia los textos. Sigue la numeración: si la última es RAT-06, esta es RAT-07. El ejemplo es de una empresa de transporte con GPS en sus camiones; bórralo o reemplázalo por tu caso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="54" t="inlineStr">
+        <is>
+          <t>Código RAT</t>
+        </is>
+      </c>
+      <c r="B4" s="54" t="inlineStr">
+        <is>
+          <t>Área / Proceso</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
+        <is>
+          <t>Categoría de Datos Personales</t>
+        </is>
+      </c>
+      <c r="D4" s="54" t="inlineStr">
+        <is>
+          <t>Titulares Afectados</t>
+        </is>
+      </c>
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>Finalidad del Tratamiento</t>
+        </is>
+      </c>
+      <c r="F4" s="54" t="inlineStr">
+        <is>
+          <t>Base Legal de Licitud</t>
+        </is>
+      </c>
+      <c r="G4" s="54" t="inlineStr">
+        <is>
+          <t>¿Datos Sensibles?</t>
+        </is>
+      </c>
+      <c r="H4" s="54" t="inlineStr">
+        <is>
+          <t>Destinatarios / Encargados Externos</t>
+        </is>
+      </c>
+      <c r="I4" s="54" t="inlineStr">
+        <is>
+          <t>Plazo de Conservación</t>
+        </is>
+      </c>
+      <c r="J4" s="54" t="inlineStr">
+        <is>
+          <t>Medidas de Seguridad Aplicadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>RAT-07</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Operaciones y transporte</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Ubicación GPS de camiones y furgones, nombre del chofer asignado</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Choferes</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Seguridad de la carga, control de ruta y atención de emergencias en carretera</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Interés legítimo del responsable en la seguridad de sus bienes; choferes informados por escrito (Anexo laboral)</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t>Proveedor del sistema GPS (con contrato de tratamiento de datos firmado)</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Mientras dure el contrato del chofer; el historial de rutas, 12 meses</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Acceso con clave personal solo para jefatura de operaciones; el GPS se usa en horario de trabajo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="51" t="inlineStr">
+        <is>
+          <t>RAT-08</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>[Área o proceso]</t>
+        </is>
+      </c>
+      <c r="C6" s="53" t="inlineStr">
+        <is>
+          <t>[Qué datos guardas]</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="inlineStr">
+        <is>
+          <t>[De quién son]</t>
+        </is>
+      </c>
+      <c r="E6" s="53" t="inlineStr">
+        <is>
+          <t>[Para qué los usas]</t>
+        </is>
+      </c>
+      <c r="F6" s="53" t="inlineStr">
+        <is>
+          <t>[Por qué puedes usarlos]</t>
+        </is>
+      </c>
+      <c r="G6" s="53" t="inlineStr">
+        <is>
+          <t>[SÍ / NO]</t>
+        </is>
+      </c>
+      <c r="H6" s="53" t="inlineStr">
+        <is>
+          <t>[Con quién los compartes]</t>
+        </is>
+      </c>
+      <c r="I6" s="53" t="inlineStr">
+        <is>
+          <t>[Cuánto tiempo los guardas]</t>
+        </is>
+      </c>
+      <c r="J6" s="53" t="inlineStr">
+        <is>
+          <t>[Cómo los proteges, solo lo que haces]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>